--- a/assets/constructions/examples/ctd_die_c2.xlsx
+++ b/assets/constructions/examples/ctd_die_c2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,11 +629,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DHS 003332-8D</t>
+          <t>TFD 30032-8D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -649,7 +669,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PALB_WC0503_H</t>
+          <t>PALB_SP07T3_H</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -658,36 +678,36 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WCKX 050308</t>
+          <t>SPKX 07T308</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>WCKX 050308</t>
+          <t>SPKX 07T308</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MDP 3508</t>
+          <t>MDP 2508</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -697,7 +717,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>PALB_WC0503H+PALB_Pilot_B:8</t>
+          <t>PALB_SP07T3H+PALB_Pilot_A:8</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -718,12 +738,12 @@
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
@@ -739,11 +759,25 @@
           <t>2020/Palbit General Catalogue</t>
         </is>
       </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1075.16</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR2" t="n">
+        <v>98843.44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DHS 003232-8D</t>
+          <t>DHS 003632-5D</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -768,7 +802,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -797,7 +831,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
@@ -833,7 +867,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -849,11 +883,25 @@
           <t>2020/Palbit General Catalogue</t>
         </is>
       </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>841.4</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR3" t="n">
+        <v>77353.02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DHS 002532-5D</t>
+          <t>TFD 22525-8D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -869,7 +917,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PALB_WС0302_H</t>
+          <t>PALB_SP0603_H</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -878,46 +926,46 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WCKX 030204</t>
+          <t>SPKX 060204</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>WCKX 030204</t>
+          <t>SPKX 060204</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MDP 3006</t>
+          <t>MDP 2006</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>ISO_9766:32</t>
+          <t>ISO_9766:25</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>PALB_WС0302H+PALB_Pilot_B:6</t>
+          <t>PALB_SP0603H+PALB_Pilot_A:6</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -934,19 +982,19 @@
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -959,11 +1007,25 @@
           <t>2020/Palbit General Catalogue</t>
         </is>
       </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>916.87</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR4" t="n">
+        <v>84291.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DHS 003532-5D</t>
+          <t>TFD 22025-8D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,7 +1041,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PALB_WC0503_H</t>
+          <t>PALB_SP0603_H</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -988,46 +1050,46 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WCKX 050308</t>
+          <t>SPKX 060204</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>WCKX 050308</t>
+          <t>SPKX 060204</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>MDP 3508</t>
+          <t>MDP 2006</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>ISO_9766:32</t>
+          <t>ISO_9766:25</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>PALB_WC0503H+PALB_Pilot_B:8</t>
+          <t>PALB_SP0603H+PALB_Pilot_A:6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1044,19 +1106,19 @@
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1069,11 +1131,25 @@
           <t>2020/Palbit General Catalogue</t>
         </is>
       </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>916.87</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR5" t="n">
+        <v>84291.25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TFD 29532-8D</t>
+          <t>DHS 003932-8D</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1089,7 +1165,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PALB_SP07T3_H</t>
+          <t>PALB_WC0503_H</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1098,36 +1174,36 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>29.5</v>
+        <v>39</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SPKX 07T308</t>
+          <t>WCKX 050308</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SPKX 07T308</t>
+          <t>WCKX 050308</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MDP 2508</t>
+          <t>MDP 3508</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
@@ -1137,7 +1213,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PALB_SP07T3H+PALB_Pilot_A:8</t>
+          <t>PALB_WC0503H+PALB_Pilot_B:8</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1158,12 +1234,12 @@
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>276</v>
+        <v>330</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
@@ -1179,6 +1255,20 @@
           <t>2020/Palbit General Catalogue</t>
         </is>
       </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1028.76</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR6" t="n">
+        <v>94577.71000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
